--- a/data/trans_camb/IP1010-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1010-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 0,0</t>
+          <t>-3,77; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,0</t>
+          <t>-3,19; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1,48</t>
+          <t>-3,58; 1,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 0,0</t>
+          <t>-4,71; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,33</t>
+          <t>-2,74; 0,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,17; -0,36</t>
+          <t>-3,01; -0,36</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,1</t>
+          <t>-0,24; 1,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,69</t>
+          <t>-0,76; 0,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,32</t>
+          <t>-0,32; 1,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,57</t>
+          <t>-0,35; 0,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,67</t>
+          <t>-0,27; 0,66</t>
         </is>
       </c>
     </row>
@@ -878,17 +878,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-65,33; —</t>
+          <t>-66,6; 1068,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,63; 612,07</t>
+          <t>-80,84; 578,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,3; 607,7</t>
+          <t>-71,88; 707,77</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,0</t>
+          <t>-2,81; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,89</t>
+          <t>-1,96; 1,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,13</t>
+          <t>-1,21; 0,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,5</t>
+          <t>-0,79; 0,51</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,62</t>
+          <t>-0,27; 0,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,11</t>
+          <t>-0,48; 0,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,26</t>
+          <t>-0,96; 0,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,71</t>
+          <t>-0,62; 0,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,26</t>
+          <t>-0,46; 0,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,36</t>
+          <t>-0,45; 0,33</t>
         </is>
       </c>
     </row>
@@ -1185,22 +1185,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-89,27; 119,04</t>
+          <t>-91,74; 113,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-70,71; 254,06</t>
+          <t>-66,61; 280,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-76,22; 141,24</t>
+          <t>-76,4; 143,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,91; 189,4</t>
+          <t>-74,07; 163,65</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1010-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1010-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,0</t>
+          <t>-2,88; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,0</t>
+          <t>-2,85; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 1,52</t>
+          <t>-3,81; 1,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 0,0</t>
+          <t>-4,78; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,36</t>
+          <t>-2,65; 0,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,01; -0,36</t>
+          <t>-3,44; -0,36</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,09</t>
+          <t>-0,15; 1,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,22</t>
+          <t>-0,47; 0,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,56</t>
+          <t>-0,74; 0,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 1,32</t>
+          <t>-0,29; 1,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,56</t>
+          <t>-0,33; 0,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,66</t>
+          <t>-0,26; 0,71</t>
         </is>
       </c>
     </row>
@@ -878,17 +878,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-66,6; 1068,0</t>
+          <t>-65,64; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-80,84; 578,05</t>
+          <t>-75,34; 811,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-71,88; 707,77</t>
+          <t>-65,15; 845,8</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,3</t>
+          <t>-1,95; 0,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,18</t>
+          <t>-1,12; 0,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,51</t>
+          <t>-0,79; 0,55</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,62</t>
+          <t>-0,28; 0,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,13</t>
+          <t>-0,5; 0,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,26</t>
+          <t>-0,92; 0,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,79</t>
+          <t>-0,65; 0,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,28</t>
+          <t>-0,46; 0,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,33</t>
+          <t>-0,41; 0,34</t>
         </is>
       </c>
     </row>
@@ -1185,22 +1185,22 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-91,74; 113,51</t>
+          <t>-88,35; 126,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-66,61; 280,46</t>
+          <t>-71,49; 240,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-76,4; 143,04</t>
+          <t>-74,34; 108,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-74,07; 163,65</t>
+          <t>-67,64; 163,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1010-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1010-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,55</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-0,71</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-0,71</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,8</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,0</t>
+          <t>-3,85; 1,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,0</t>
+          <t>-4,77; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 1,49</t>
+          <t>-4,61; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 0,0</t>
+          <t>-3,55; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,35</t>
+          <t>-2,59; 0,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,44; -0,36</t>
+          <t>-3,17; -0,36</t>
         </is>
       </c>
     </row>
@@ -669,17 +669,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-51,72%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-51,72%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,02</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,44</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,22</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,03</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,12</t>
+          <t>-0,69; 0,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,22</t>
+          <t>-0,29; 1,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,66</t>
+          <t>-0,15; 1,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,29</t>
+          <t>-0,58; 0,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,62</t>
+          <t>-0,35; 0,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,71</t>
+          <t>-0,24; 0,67</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-3,81%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>102,83%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>152,53%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-23,74%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-3,81%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>102,83%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-65,33; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -878,17 +878,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-65,64; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,34; 811,99</t>
+          <t>-70,63; 612,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,15; 845,8</t>
+          <t>-64,3; 607,7</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,81</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,37</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,27</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>-2,79; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,03; 0,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,0</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,13</t>
+          <t>-1,01; 0,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,55</t>
+          <t>-0,77; 0,5</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-45,9%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-45,9%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,03</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,11</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,11</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,61</t>
+          <t>-0,93; 0,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,12</t>
+          <t>-0,65; 0,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,25</t>
+          <t>-0,26; 0,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,78</t>
+          <t>-0,46; 0,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,25</t>
+          <t>-0,47; 0,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,34</t>
+          <t>-0,4; 0,36</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-45,07%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>61,82%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-59,38%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-45,07%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,27; 119,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-70,71; 254,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-88,35; 126,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-71,49; 240,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-74,34; 108,6</t>
+          <t>-76,22; 141,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,64; 163,54</t>
+          <t>-66,91; 189,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1010-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1010-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,281 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,8</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,55</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,71</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,71</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,76</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,12</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.7994727934616739</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.545858946414424</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.7062861718131215</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.7062861718131215</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.7611450457224762</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-1.116570320046377</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,85; 1,48</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-4,77; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,61; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-3,55; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-2,59; 0,33</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-3,17; -0,36</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.853704001115793</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.765906597215934</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.606213835576606</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-3.554580446855186</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-2.58738922455979</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-3.174574384565402</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-51,72%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-68,17%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.477028220793954</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.3347492943427062</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>-0.3569825747053485</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>-0.5171705965256586</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.68168124484167</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,03</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,2</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,69; 0,69</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,29; 1,32</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,15; 1,1</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-0,58; 0,22</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-0,35; 0,57</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-0,24; 0,67</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-3,81%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>102,83%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>152,53%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-23,74%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>31,79%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>67,35%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>-0.01630506800877193</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.4397480741153363</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.2218529823122767</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.03452663564228219</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.09414980500771181</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.1994606625188228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-65,33; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-70,63; 612,07</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-64,3; 607,7</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.6945434063536529</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.2857574552129916</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.1457118693790629</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.5820167966632933</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.3513537849672494</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.2414456396000656</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,25</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.6913933956756351</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.321272398489314</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.103124837564532</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.2216923429313449</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.5713443439197324</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.6667865120514918</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,79; 0,0</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,03; 0,89</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,3</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-1,01; 0,13</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-0,77; 0,5</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>-0.0381271109190017</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1.028289093255712</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1.525321872254195</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.2373834778853454</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.3178901713081075</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.6734648486222948</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-45,9%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-65,76%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-40,85%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="n">
+        <v>-0.6533044950416023</v>
+      </c>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="n">
+        <v>-0.7063288880106271</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.6430401045846168</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="n">
+        <v>6.120707936896956</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>6.076951925638713</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +882,281 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-0.8065428446572515</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.3702346688995722</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.2678300614319545</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.2524936840922775</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.1568228186888691</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,93; 0,26</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,65; 0,71</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,26; 0,62</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-0,46; 0,11</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-0,47; 0,26</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-0,4; 0,36</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.787046564728278</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.032128574846716</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="n">
+        <v>-1.01484878506982</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.7718741192616022</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-45,07%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>61,82%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-59,38%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-22,51%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-8,49%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.8897370022928178</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.29607633048371</v>
+      </c>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="n">
+        <v>0.1334127225988891</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.5009658439824665</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-89,27; 119,04</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-70,71; 254,06</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-76,22; 141,24</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-66,91; 189,4</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.4590390595516438</v>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="n">
+        <v>-0.657645311959003</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.4084608765153893</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.2907695396076166</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.03383088733612877</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.1131898583950511</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.1087293192786055</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.09472306860990949</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.03575006333340655</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.9335688095859938</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.6484104198708626</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.2644707725922421</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.4602953615956213</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.4712093962388993</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.3954553395441769</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.2572805151251269</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.7107071133657</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.6192331375398711</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.1148865521396976</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.2595910798416614</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.3567839960296612</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>-0.4507019955409771</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.05243894685079935</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.6181770139621666</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.5938161499168914</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.2250655515733407</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.08494348674503625</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>-0.8927135369173184</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.707099386078459</v>
+      </c>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="n">
+        <v>-0.7621673078931873</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.669120442132203</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>1.190389890848613</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>2.540568528409352</v>
+      </c>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="n">
+        <v>1.412393705321423</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1.893959539870729</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1164,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
